--- a/2022ui_autotest/Kuajing/Little_tools/需求维度/23电商结汇明细上传/custom-电商收款-通用--一列1个商品-EUR.xlsx
+++ b/2022ui_autotest/Kuajing/Little_tools/需求维度/23电商结汇明细上传/custom-电商收款-通用--一列1个商品-EUR.xlsx
@@ -22,7 +22,7 @@
     <t>订单号*</t>
   </si>
   <si>
-    <t>only202602030005</t>
+    <t>only20260204005</t>
   </si>
   <si>
     <t>交易时间（YYYY-MM-DD HH:MM:SS）*</t>
